--- a/sources/table_normalization/xlsx/economy-table34.xlsx
+++ b/sources/table_normalization/xlsx/economy-table34.xlsx
@@ -119,22 +119,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -625,63 +625,63 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="7" t="s">
+      <c r="I1" s="8"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1"/>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
